--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -3113,6 +3113,68 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260927-064918-6984E827</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تلگرام ادز با شروع دیجی پی</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">digipay_digipay_panel_mehr_1405</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">digipay</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">digipay_panel</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mehr</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-27</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-27T06:49:18.063Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -4631,7 +4693,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T11:28:01.466096+00:00</t>
+          <t xml:space="preserve">2026-09-27T06:49:27.219368+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,57 +161,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260908-112751-C889CFF2</t>
+          <t xml:space="preserve">UTM-260927-065151-3E19E7D0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260908-111715-8FB3E495</t>
+          <t xml:space="preserve">CMP-260927-064918-6984E827</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین جذب فول فاند پرو شهریورماه</t>
+          <t xml:space="preserve">تلگرام ادز با شروع دیجی پی</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfund_pro_iran_broker_topic_shahrivar_1405</t>
+          <t xml:space="preserve">digipay_digipay_panel_mehr_1405</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">کامیونیتی ایران بروکر</t>
+          <t xml:space="preserve">تلگرام</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https_forum_iranbroker_net</t>
+          <t xml:space="preserve">telegram</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">تبلیغات بنری</t>
+          <t xml:space="preserve">سوشال — رسانه‌های خودمان</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">display</t>
+          <t xml:space="preserve">owned_social</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260908-112705-05380120</t>
+          <t xml:space="preserve">CR-260901-110923-EE09CA3B</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">تاپیک ایران بروکر</t>
+          <t xml:space="preserve">inner link</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260908_112705_05380120_v1</t>
+          <t xml:space="preserve">text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -231,17 +231,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=https_forum_iranbroker_net&amp;utm_medium=display&amp;utm_campaign=fullfund_pro_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260908_112705_05380120_v1</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=telegram&amp;utm_medium=owned_social&amp;utm_campaign=digipay_digipay_panel_mehr_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">کامیونیتی ایران بروکر</t>
+          <t xml:space="preserve">کانال شبکه‌های اجتماعی رابین‌سود</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-27</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -256,7 +256,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T11:27:51.066Z</t>
+          <t xml:space="preserve">2026-09-27T06:51:51.962Z</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -273,57 +273,57 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-111838-F1589F42</t>
+          <t xml:space="preserve">UTM-260908-112751-C889CFF2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260831-200113-3FFD5992</t>
+          <t xml:space="preserve">CMP-260908-111715-8FB3E495</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو شهریورماه</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+          <t xml:space="preserve">fullfund_pro_iran_broker_topic_shahrivar_1405</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">عصر قلم</t>
+          <t xml:space="preserve">کامیونیتی ایران بروکر</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https_asreqalam_com</t>
+          <t xml:space="preserve">https_forum_iranbroker_net</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">رفرال</t>
+          <t xml:space="preserve">تبلیغات بنری</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">referral</t>
+          <t xml:space="preserve">display</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260901-110923-EE09CA3B</t>
+          <t xml:space="preserve">CR-260908-112705-05380120</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inner link</t>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260901_110923_ee09ca3b_v1</t>
+          <t xml:space="preserve">text_cr_260908_112705_05380120_v1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -338,22 +338,22 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=https_forum_iranbroker_net&amp;utm_medium=display&amp;utm_campaign=fullfund_pro_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260908_112705_05380120_v1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 عدد گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کامیونیتی ایران بروکر</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -368,7 +368,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T11:18:38.884Z</t>
+          <t xml:space="preserve">2026-09-08T11:27:51.066Z</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -385,7 +385,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-111516-E7335995</t>
+          <t xml:space="preserve">UTM-260901-111838-F1589F42</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -450,12 +450,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T11:15:16.634Z</t>
+          <t xml:space="preserve">2026-09-01T11:18:38.884Z</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-111033-45E08A6B</t>
+          <t xml:space="preserve">UTM-260901-111516-E7335995</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -562,12 +562,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T11:10:33.037Z</t>
+          <t xml:space="preserve">2026-09-01T11:15:16.634Z</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -609,57 +609,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-085808-9F62A258</t>
+          <t xml:space="preserve">UTM-260901-111033-45E08A6B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260901-085307-6BB54908</t>
+          <t xml:space="preserve">CMP-260831-200113-3FFD5992</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین تلگرام ادز</t>
+          <t xml:space="preserve">کمپین گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfundpro_lead_generation_shahrivar_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">تلگرام</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">https_asreqalam_com</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">سوشال رسمی / تبلیغات پلتفرمی</t>
+          <t xml:space="preserve">رفرال</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">platform_ads</t>
+          <t xml:space="preserve">referral</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260901-085439-FE513724</t>
+          <t xml:space="preserve">CR-260901-110923-EE09CA3B</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">لندینگ اصلی رابین سود نسخه 1</t>
+          <t xml:space="preserve">inner link</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">landing_cr_260901_085439_fe513724_v1</t>
+          <t xml:space="preserve">text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -674,17 +674,17 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://landing.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://landing.robinsood.com/?utm_source=telegram&amp;utm_medium=platform_ads&amp;utm_campaign=fullfundpro_lead_generation_shahrivar_1405&amp;utm_content=landing_cr_260901_085439_fe513724_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">5 عدد گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -694,17 +694,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t xml:space="preserve">مدیر اصلی</t>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t xml:space="preserve">owner</t>
+          <t xml:space="preserve">marketing</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T08:58:08.438Z</t>
+          <t xml:space="preserve">2026-09-01T11:10:33.037Z</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -721,57 +721,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-061312-E59AAE83</t>
+          <t xml:space="preserve">UTM-260901-085808-9F62A258</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260831-191708-22583F97</t>
+          <t xml:space="preserve">CMP-260901-085307-6BB54908</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین sms  مارکتنیگ افزایش لید فول فاند پرو شهریور</t>
+          <t xml:space="preserve">کمپین تلگرام ادز</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfund_pro_najva_shahrivar_1405</t>
+          <t xml:space="preserve">fullfundpro_lead_generation_shahrivar_1405</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا پیامک</t>
+          <t xml:space="preserve">تلگرام</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">site-https_www_najva_com</t>
+          <t xml:space="preserve">telegram</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیامک</t>
+          <t xml:space="preserve">سوشال رسمی / تبلیغات پلتفرمی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms</t>
+          <t xml:space="preserve">platform_ads</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260831-191951-166E33F1</t>
+          <t xml:space="preserve">CR-260901-085439-FE513724</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">لندینگ آموزشی پیامک نجوا لیدگیری فول فاند پرو</t>
+          <t xml:space="preserve">لندینگ اصلی رابین سود نسخه 1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">landing_cr_260831_191951_166e33f1_v1</t>
+          <t xml:space="preserve">landing_cr_260901_085439_fe513724_v1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://landing.robinsood.com/</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=site-https_www_najva_com&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
+          <t xml:space="preserve">https://landing.robinsood.com/?utm_source=telegram&amp;utm_medium=platform_ads&amp;utm_campaign=fullfundpro_lead_generation_shahrivar_1405&amp;utm_content=landing_cr_260901_085439_fe513724_v1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T06:13:12.719Z</t>
+          <t xml:space="preserve">2026-09-01T08:58:08.438Z</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260831-192118-35297D77</t>
+          <t xml:space="preserve">UTM-260901-061312-E59AAE83</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیامک — نجوا</t>
+          <t xml:space="preserve">سایت نجوا پیامک</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms_najva</t>
+          <t xml:space="preserve">site-https_www_najva_com</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -898,37 +898,37 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=sms_najva&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=site-https_www_najva_com&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAJVA _ YEKTANET</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t xml:space="preserve">مسئول مارکتینگ</t>
+          <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t xml:space="preserve">marketing</t>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-31T19:21:18.902Z</t>
+          <t xml:space="preserve">2026-09-01T06:13:12.719Z</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -945,57 +945,57 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260827-125155-21514E11</t>
+          <t xml:space="preserve">UTM-260831-192118-35297D77</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260827-125038-911A460E</t>
+          <t xml:space="preserve">CMP-260831-191708-22583F97</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
+          <t xml:space="preserve">کمپین sms  مارکتنیگ افزایش لید فول فاند پرو شهریور</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
+          <t xml:space="preserve">fullfund_pro_najva_shahrivar_1405</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا</t>
+          <t xml:space="preserve">پیامک — نجوا</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">site-https_app_cmercury_com</t>
+          <t xml:space="preserve">sms_najva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">سوشال — رسانه دیگران (تبلیغ پولی)</t>
+          <t xml:space="preserve">پیامک</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">paid_social</t>
+          <t xml:space="preserve">sms</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260827-124734-652CA150</t>
+          <t xml:space="preserve">CR-260831-191951-166E33F1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
+          <t xml:space="preserve">لندینگ آموزشی پیامک نجوا لیدگیری فول فاند پرو</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">landing_cr_260827_124734_652ca150_v1</t>
+          <t xml:space="preserve">landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1015,32 +1015,32 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_social&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=landing_cr_260827_124734_652ca150_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=sms_najva&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا برای ارسال ایمیل</t>
+          <t xml:space="preserve">NAJVA _ YEKTANET</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t xml:space="preserve">مدیر اصلی</t>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t xml:space="preserve">owner</t>
+          <t xml:space="preserve">marketing</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T12:51:55.977Z</t>
+          <t xml:space="preserve">2026-08-31T19:21:18.902Z</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1057,12 +1057,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
+          <t xml:space="preserve">UTM-260827-125155-21514E11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
+          <t xml:space="preserve">CMP-260827-125038-911A460E</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1087,17 +1087,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">رفرال</t>
+          <t xml:space="preserve">سوشال — رسانه دیگران (تبلیغ پولی)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">paid_referral</t>
+          <t xml:space="preserve">paid_social</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
+          <t xml:space="preserve">CR-260827-124734-652CA150</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
+          <t xml:space="preserve">landing_cr_260827_124734_652ca150_v1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_social&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=landing_cr_260827_124734_652ca150_v1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
+          <t xml:space="preserve">2026-08-27T12:51:55.977Z</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1169,57 +1169,57 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
+          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVOSH</t>
+          <t xml:space="preserve">سایت نجوا</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">chavosh</t>
+          <t xml:space="preserve">site-https_app_cmercury_com</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVOSH</t>
+          <t xml:space="preserve">رفرال</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">chavosh</t>
+          <t xml:space="preserve">paid_referral</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1234,37 +1234,37 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">سایت نجوا برای ارسال ایمیل</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25</t>
+          <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t xml:space="preserve">مسئول مارکتینگ</t>
+          <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t xml:space="preserve">marketing</t>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
+          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
+          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
+          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
+          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1505,7 +1505,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
+          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
+          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
+          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1729,7 +1729,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
+          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
+          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1841,57 +1841,57 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
+          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">IranBroker</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">iranbroker</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایران بروکر</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">topic</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تاپیک ایران بروکر</t>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
+          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1953,57 +1953,57 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
+          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">عصر قلم</t>
+          <t xml:space="preserve">IranBroker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">iranbroker</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ریپورتاژ</t>
+          <t xml:space="preserve">ایران بروکر</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">topic</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
+          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2065,7 +2065,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
+          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
+          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2177,7 +2177,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
+          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
+          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2289,57 +2289,57 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">ریپورتاژ</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام متنی کانال</t>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram channel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2401,7 +2401,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
@@ -2466,12 +2466,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2625,110 +2625,222 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
+      <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
+      <c r="P25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4693,7 +4805,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-27T06:49:27.219368+00:00</t>
+          <t xml:space="preserve">2026-09-27T06:54:09.960065+00:00</t>
         </is>
       </c>
     </row>
@@ -4705,7 +4817,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -4749,6 +4749,53 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260927-080156-0BC8A7B3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لندینگ ایمیل مارکتینگ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">landing_cr_260927_080156_0bc8a7b3_v1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-260827-124724-E0E58232</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-27T08:01:56.275Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -4805,7 +4852,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-27T06:54:09.960065+00:00</t>
+          <t xml:space="preserve">2026-09-27T08:02:04.223255+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -3287,6 +3287,68 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260927-080312-EDECD02E</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کمپین فروش چالش با رونمایی دیجی پی و ریدیزاین سامانه پگاه</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">digipay_panel_digipay_panel_mehr_1405</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">digipay_panel</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">digipay_panel</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mehr</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-27</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-27T08:03:12.494Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -4852,7 +4914,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-27T08:02:04.223255+00:00</t>
+          <t xml:space="preserve">2026-09-27T08:03:21.816619+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,57 +161,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260927-065151-3E19E7D0</t>
+          <t xml:space="preserve">UTM-260927-080346-D2D6D1D7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260927-064918-6984E827</t>
+          <t xml:space="preserve">CMP-260927-080312-EDECD02E</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">تلگرام ادز با شروع دیجی پی</t>
+          <t xml:space="preserve">کمپین فروش چالش با رونمایی دیجی پی و ریدیزاین سامانه پگاه</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">digipay_digipay_panel_mehr_1405</t>
+          <t xml:space="preserve">digipay_panel_digipay_panel_mehr_1405</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">تلگرام</t>
+          <t xml:space="preserve">ایمیل — Mercury</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">email_mercury</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">سوشال — رسانه‌های خودمان</t>
+          <t xml:space="preserve">ایمیل</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">owned_social</t>
+          <t xml:space="preserve">email</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260901-110923-EE09CA3B</t>
+          <t xml:space="preserve">CR-260927-080156-0BC8A7B3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">inner link</t>
+          <t xml:space="preserve">لندینگ ایمیل مارکتینگ</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260901_110923_ee09ca3b_v1</t>
+          <t xml:space="preserve">landing_cr_260927_080156_0bc8a7b3_v1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -231,12 +231,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=telegram&amp;utm_medium=owned_social&amp;utm_campaign=digipay_digipay_panel_mehr_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=email_mercury&amp;utm_medium=email&amp;utm_campaign=digipay_panel_digipay_panel_mehr_1405&amp;utm_content=landing_cr_260927_080156_0bc8a7b3_v1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">کانال شبکه‌های اجتماعی رابین‌سود</t>
+          <t xml:space="preserve">ایمیل کاربران خودمان در مرکوری نجوا</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -256,7 +256,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-27T06:51:51.962Z</t>
+          <t xml:space="preserve">2026-09-27T08:03:46.717Z</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -273,57 +273,57 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260908-112751-C889CFF2</t>
+          <t xml:space="preserve">UTM-260927-065151-3E19E7D0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260908-111715-8FB3E495</t>
+          <t xml:space="preserve">CMP-260927-064918-6984E827</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین جذب فول فاند پرو شهریورماه</t>
+          <t xml:space="preserve">تلگرام ادز با شروع دیجی پی</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfund_pro_iran_broker_topic_shahrivar_1405</t>
+          <t xml:space="preserve">digipay_digipay_panel_mehr_1405</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">کامیونیتی ایران بروکر</t>
+          <t xml:space="preserve">تلگرام</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https_forum_iranbroker_net</t>
+          <t xml:space="preserve">telegram</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">تبلیغات بنری</t>
+          <t xml:space="preserve">سوشال — رسانه‌های خودمان</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">display</t>
+          <t xml:space="preserve">owned_social</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260908-112705-05380120</t>
+          <t xml:space="preserve">CR-260901-110923-EE09CA3B</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">تاپیک ایران بروکر</t>
+          <t xml:space="preserve">inner link</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260908_112705_05380120_v1</t>
+          <t xml:space="preserve">text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -343,17 +343,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=https_forum_iranbroker_net&amp;utm_medium=display&amp;utm_campaign=fullfund_pro_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260908_112705_05380120_v1</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=telegram&amp;utm_medium=owned_social&amp;utm_campaign=digipay_digipay_panel_mehr_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">کامیونیتی ایران بروکر</t>
+          <t xml:space="preserve">کانال شبکه‌های اجتماعی رابین‌سود</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-27</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -368,7 +368,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T11:27:51.066Z</t>
+          <t xml:space="preserve">2026-09-27T06:51:51.962Z</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -385,57 +385,57 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-111838-F1589F42</t>
+          <t xml:space="preserve">UTM-260908-112751-C889CFF2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260831-200113-3FFD5992</t>
+          <t xml:space="preserve">CMP-260908-111715-8FB3E495</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو شهریورماه</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+          <t xml:space="preserve">fullfund_pro_iran_broker_topic_shahrivar_1405</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">عصر قلم</t>
+          <t xml:space="preserve">کامیونیتی ایران بروکر</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https_asreqalam_com</t>
+          <t xml:space="preserve">https_forum_iranbroker_net</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">رفرال</t>
+          <t xml:space="preserve">تبلیغات بنری</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">referral</t>
+          <t xml:space="preserve">display</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260901-110923-EE09CA3B</t>
+          <t xml:space="preserve">CR-260908-112705-05380120</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">inner link</t>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260901_110923_ee09ca3b_v1</t>
+          <t xml:space="preserve">text_cr_260908_112705_05380120_v1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -450,22 +450,22 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=https_forum_iranbroker_net&amp;utm_medium=display&amp;utm_campaign=fullfund_pro_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260908_112705_05380120_v1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 عدد گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کامیونیتی ایران بروکر</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T11:18:38.884Z</t>
+          <t xml:space="preserve">2026-09-08T11:27:51.066Z</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-111516-E7335995</t>
+          <t xml:space="preserve">UTM-260901-111838-F1589F42</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -562,12 +562,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T11:15:16.634Z</t>
+          <t xml:space="preserve">2026-09-01T11:18:38.884Z</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-111033-45E08A6B</t>
+          <t xml:space="preserve">UTM-260901-111516-E7335995</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T11:10:33.037Z</t>
+          <t xml:space="preserve">2026-09-01T11:15:16.634Z</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -721,57 +721,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-085808-9F62A258</t>
+          <t xml:space="preserve">UTM-260901-111033-45E08A6B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260901-085307-6BB54908</t>
+          <t xml:space="preserve">CMP-260831-200113-3FFD5992</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین تلگرام ادز</t>
+          <t xml:space="preserve">کمپین گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfundpro_lead_generation_shahrivar_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">تلگرام</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">https_asreqalam_com</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">سوشال رسمی / تبلیغات پلتفرمی</t>
+          <t xml:space="preserve">رفرال</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">platform_ads</t>
+          <t xml:space="preserve">referral</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260901-085439-FE513724</t>
+          <t xml:space="preserve">CR-260901-110923-EE09CA3B</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">لندینگ اصلی رابین سود نسخه 1</t>
+          <t xml:space="preserve">inner link</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">landing_cr_260901_085439_fe513724_v1</t>
+          <t xml:space="preserve">text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -786,17 +786,17 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://landing.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://landing.robinsood.com/?utm_source=telegram&amp;utm_medium=platform_ads&amp;utm_campaign=fullfundpro_lead_generation_shahrivar_1405&amp;utm_content=landing_cr_260901_085439_fe513724_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">5 عدد گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -806,17 +806,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t xml:space="preserve">مدیر اصلی</t>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t xml:space="preserve">owner</t>
+          <t xml:space="preserve">marketing</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T08:58:08.438Z</t>
+          <t xml:space="preserve">2026-09-01T11:10:33.037Z</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -833,57 +833,57 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-061312-E59AAE83</t>
+          <t xml:space="preserve">UTM-260901-085808-9F62A258</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260831-191708-22583F97</t>
+          <t xml:space="preserve">CMP-260901-085307-6BB54908</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین sms  مارکتنیگ افزایش لید فول فاند پرو شهریور</t>
+          <t xml:space="preserve">کمپین تلگرام ادز</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfund_pro_najva_shahrivar_1405</t>
+          <t xml:space="preserve">fullfundpro_lead_generation_shahrivar_1405</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا پیامک</t>
+          <t xml:space="preserve">تلگرام</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">site-https_www_najva_com</t>
+          <t xml:space="preserve">telegram</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیامک</t>
+          <t xml:space="preserve">سوشال رسمی / تبلیغات پلتفرمی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms</t>
+          <t xml:space="preserve">platform_ads</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260831-191951-166E33F1</t>
+          <t xml:space="preserve">CR-260901-085439-FE513724</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">لندینگ آموزشی پیامک نجوا لیدگیری فول فاند پرو</t>
+          <t xml:space="preserve">لندینگ اصلی رابین سود نسخه 1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">landing_cr_260831_191951_166e33f1_v1</t>
+          <t xml:space="preserve">landing_cr_260901_085439_fe513724_v1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://landing.robinsood.com/</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=site-https_www_najva_com&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
+          <t xml:space="preserve">https://landing.robinsood.com/?utm_source=telegram&amp;utm_medium=platform_ads&amp;utm_campaign=fullfundpro_lead_generation_shahrivar_1405&amp;utm_content=landing_cr_260901_085439_fe513724_v1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T06:13:12.719Z</t>
+          <t xml:space="preserve">2026-09-01T08:58:08.438Z</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -945,7 +945,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260831-192118-35297D77</t>
+          <t xml:space="preserve">UTM-260901-061312-E59AAE83</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیامک — نجوا</t>
+          <t xml:space="preserve">سایت نجوا پیامک</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms_najva</t>
+          <t xml:space="preserve">site-https_www_najva_com</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1010,37 +1010,37 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=sms_najva&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=site-https_www_najva_com&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAJVA _ YEKTANET</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t xml:space="preserve">مسئول مارکتینگ</t>
+          <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t xml:space="preserve">marketing</t>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-31T19:21:18.902Z</t>
+          <t xml:space="preserve">2026-09-01T06:13:12.719Z</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1057,57 +1057,57 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260827-125155-21514E11</t>
+          <t xml:space="preserve">UTM-260831-192118-35297D77</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260827-125038-911A460E</t>
+          <t xml:space="preserve">CMP-260831-191708-22583F97</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
+          <t xml:space="preserve">کمپین sms  مارکتنیگ افزایش لید فول فاند پرو شهریور</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
+          <t xml:space="preserve">fullfund_pro_najva_shahrivar_1405</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا</t>
+          <t xml:space="preserve">پیامک — نجوا</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">site-https_app_cmercury_com</t>
+          <t xml:space="preserve">sms_najva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">سوشال — رسانه دیگران (تبلیغ پولی)</t>
+          <t xml:space="preserve">پیامک</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">paid_social</t>
+          <t xml:space="preserve">sms</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260827-124734-652CA150</t>
+          <t xml:space="preserve">CR-260831-191951-166E33F1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
+          <t xml:space="preserve">لندینگ آموزشی پیامک نجوا لیدگیری فول فاند پرو</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">landing_cr_260827_124734_652ca150_v1</t>
+          <t xml:space="preserve">landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1127,32 +1127,32 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_social&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=landing_cr_260827_124734_652ca150_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=sms_najva&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا برای ارسال ایمیل</t>
+          <t xml:space="preserve">NAJVA _ YEKTANET</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t xml:space="preserve">مدیر اصلی</t>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t xml:space="preserve">owner</t>
+          <t xml:space="preserve">marketing</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T12:51:55.977Z</t>
+          <t xml:space="preserve">2026-08-31T19:21:18.902Z</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1169,12 +1169,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
+          <t xml:space="preserve">UTM-260827-125155-21514E11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
+          <t xml:space="preserve">CMP-260827-125038-911A460E</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">رفرال</t>
+          <t xml:space="preserve">سوشال — رسانه دیگران (تبلیغ پولی)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">paid_referral</t>
+          <t xml:space="preserve">paid_social</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
+          <t xml:space="preserve">CR-260827-124734-652CA150</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
+          <t xml:space="preserve">landing_cr_260827_124734_652ca150_v1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_social&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=landing_cr_260827_124734_652ca150_v1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
+          <t xml:space="preserve">2026-08-27T12:51:55.977Z</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1281,57 +1281,57 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
+          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVOSH</t>
+          <t xml:space="preserve">سایت نجوا</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">chavosh</t>
+          <t xml:space="preserve">site-https_app_cmercury_com</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVOSH</t>
+          <t xml:space="preserve">رفرال</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">chavosh</t>
+          <t xml:space="preserve">paid_referral</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1346,37 +1346,37 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">سایت نجوا برای ارسال ایمیل</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25</t>
+          <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t xml:space="preserve">مسئول مارکتینگ</t>
+          <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t xml:space="preserve">marketing</t>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
+          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
+          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
+          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1505,7 +1505,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
+          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
+          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1729,7 +1729,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
+          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
+          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1841,7 +1841,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
+          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
+          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1953,57 +1953,57 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
+          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">IranBroker</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">iranbroker</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایران بروکر</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">topic</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">تاپیک ایران بروکر</t>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
+          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2065,57 +2065,57 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
+          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">عصر قلم</t>
+          <t xml:space="preserve">IranBroker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">iranbroker</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ریپورتاژ</t>
+          <t xml:space="preserve">ایران بروکر</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">topic</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
+          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2177,7 +2177,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
+          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
+          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2289,7 +2289,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
+          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
+          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2401,57 +2401,57 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">ریپورتاژ</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام متنی کانال</t>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2466,17 +2466,17 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram channel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2533,24 +2533,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2625,7 +2625,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2737,110 +2737,222 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
+      <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
+      <c r="P26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4914,7 +5026,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-27T08:03:21.816619+00:00</t>
+          <t xml:space="preserve">2026-09-27T08:03:55.502475+00:00</t>
         </is>
       </c>
     </row>
@@ -4926,7 +5038,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
     </row>
@@ -4938,7 +5050,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
     </row>
